--- a/app/data/card_list.xlsx
+++ b/app/data/card_list.xlsx
@@ -11977,8 +11977,8 @@
       <c r="K53" t="str">
         <v>무색1</v>
       </c>
-      <c r="M53">
-        <v>0</v>
+      <c r="M53" t="str">
+        <v>20×</v>
       </c>
       <c r="O53">
         <v>1</v>
@@ -12059,8 +12059,8 @@
       <c r="K55" t="str">
         <v>무색4</v>
       </c>
-      <c r="M55">
-        <v>50</v>
+      <c r="M55" t="str">
+        <v>50+</v>
       </c>
       <c r="O55">
         <v>4</v>
@@ -12451,8 +12451,8 @@
       <c r="K65" t="str">
         <v>무색3</v>
       </c>
-      <c r="M65">
-        <v>70</v>
+      <c r="M65" t="str">
+        <v>70+</v>
       </c>
       <c r="O65">
         <v>2</v>
@@ -12907,8 +12907,8 @@
       <c r="K77" t="str">
         <v>무색3</v>
       </c>
-      <c r="M77">
-        <v>50</v>
+      <c r="M77" t="str">
+        <v>50+</v>
       </c>
       <c r="O77">
         <v>2</v>
@@ -13059,8 +13059,8 @@
       <c r="K81" t="str">
         <v>무색1</v>
       </c>
-      <c r="M81">
-        <v>20</v>
+      <c r="M81" t="str">
+        <v>20+</v>
       </c>
       <c r="O81">
         <v>1</v>
@@ -13661,8 +13661,8 @@
       <c r="K97" t="str">
         <v>무색1</v>
       </c>
-      <c r="M97">
-        <v>20</v>
+      <c r="M97" t="str">
+        <v>20+</v>
       </c>
       <c r="O97">
         <v>2</v>
@@ -13702,8 +13702,8 @@
       <c r="K98" t="str">
         <v>무색2</v>
       </c>
-      <c r="M98">
-        <v>50</v>
+      <c r="M98" t="str">
+        <v>50+</v>
       </c>
       <c r="O98">
         <v>1</v>
@@ -17813,7 +17813,7 @@
         <v>번개</v>
       </c>
       <c r="S200" t="str">
-        <v>스태디움 기반 피해</v>
+        <v>스타디움 기반 피해</v>
       </c>
       <c r="T200" t="str">
         <v>몽환퍼레이드</v>
@@ -20572,8 +20572,8 @@
         <v>이브이 가방</v>
       </c>
       <c r="D60" t="str" xml:space="preserve">
-        <v xml:space="preserve">이 카드는 2가지 효과에서 1가지를 선택해서 사용한다. _x000d__x000d__x000d_
-① 이 차례에 자신의 「이브이」에서 진화하는 포켓몬이 사용하는 기술이 상대의 배틀 포켓몬에게 주는 데미지를 +10한다. _x000d__x000d__x000d_
+        <v xml:space="preserve">이 카드는 2가지 효과에서 1가지를 선택해서 사용한다. _x000d__x000d__x000d__x000d__x000d__x000d_
+① 이 차례에 자신의 「이브이」에서 진화하는 포켓몬이 사용하는 기술이 상대의 배틀 포켓몬에게 주는 데미지를 +10한다. _x000d__x000d__x000d__x000d__x000d__x000d_
 ② 자신의 「이브이」에서 진호하는 포켓몬 전원의 HP를 20회복.  </v>
       </c>
       <c r="E60" t="str">
@@ -21834,11 +21834,2021 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetData/>
+  <dimension ref="A1:T51"/>
+  <cols>
+    <col min="4" max="4" customWidth="1" width="11.33203125"/>
+    <col min="9" max="9" customWidth="1" width="21.88671875"/>
+    <col min="10" max="10" customWidth="1" width="28.77734375"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" t="str">
+        <v>타입</v>
+      </c>
+      <c r="B1" t="str">
+        <v>ID</v>
+      </c>
+      <c r="C1" t="str">
+        <v>속성</v>
+      </c>
+      <c r="D1" t="str">
+        <v>이름</v>
+      </c>
+      <c r="E1" t="str">
+        <v>진화</v>
+      </c>
+      <c r="F1" t="str">
+        <v>HP</v>
+      </c>
+      <c r="G1" t="str">
+        <v>기술명</v>
+      </c>
+      <c r="H1" t="str">
+        <v>기술명2</v>
+      </c>
+      <c r="I1" t="str">
+        <v>기술추가효과</v>
+      </c>
+      <c r="J1" t="str">
+        <v>기술추가효과2</v>
+      </c>
+      <c r="K1" t="str">
+        <v>기술에너지</v>
+      </c>
+      <c r="L1" t="str">
+        <v>기술에너지2</v>
+      </c>
+      <c r="M1" t="str">
+        <v>피해량</v>
+      </c>
+      <c r="N1" t="str">
+        <v>피해량2</v>
+      </c>
+      <c r="O1" t="str">
+        <v>후퇴에너지</v>
+      </c>
+      <c r="P1" t="str">
+        <v>특성</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>특성효과</v>
+      </c>
+      <c r="R1" t="str">
+        <v>약점</v>
+      </c>
+      <c r="S1" t="str">
+        <v>키워드</v>
+      </c>
+      <c r="T1" t="str">
+        <v>확장팩</v>
+      </c>
+    </row>
+    <row r="2" ht="17.25" customHeight="1">
+      <c r="A2" t="str">
+        <v>아이템</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Z00001</v>
+      </c>
+      <c r="D2" t="str">
+        <v>상처약</v>
+      </c>
+      <c r="I2" t="str">
+        <v>자신의 포켓몬 1마리의 HP를 20회복</v>
+      </c>
+      <c r="S2" t="str">
+        <v>자신 회복</v>
+      </c>
+      <c r="T2" t="str">
+        <v>프로모</v>
+      </c>
+    </row>
+    <row r="3" ht="17.25" customHeight="1">
+      <c r="A3" t="str">
+        <v>아이템</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Z00002</v>
+      </c>
+      <c r="D3" t="str">
+        <v>스피드업</v>
+      </c>
+      <c r="I3" t="str">
+        <v>이 차례에 자신의 배틀 포켓몬의 후퇴에 필요한 에너지를 1개 적게 만든다.</v>
+      </c>
+      <c r="S3" t="str">
+        <v>후퇴비용 감소</v>
+      </c>
+      <c r="T3" t="str">
+        <v>프로모</v>
+      </c>
+    </row>
+    <row r="4" ht="17.25" customHeight="1">
+      <c r="A4" t="str">
+        <v>아이템</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Z00003</v>
+      </c>
+      <c r="D4" t="str">
+        <v>핸드스코프</v>
+      </c>
+      <c r="I4" t="str">
+        <v>상대의 패의 앞면을 모두 본다.</v>
+      </c>
+      <c r="S4" t="str">
+        <v>패 확인</v>
+      </c>
+      <c r="T4" t="str">
+        <v>프로모</v>
+      </c>
+    </row>
+    <row r="5" ht="17.25" customHeight="1">
+      <c r="A5" t="str">
+        <v>아이템</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Z00004</v>
+      </c>
+      <c r="D5" t="str">
+        <v>포켓몬 도감</v>
+      </c>
+      <c r="I5" t="str">
+        <v>자신의 덱을 위에서부터 3장 보고 원래대로 되돌린다.</v>
+      </c>
+      <c r="S5" t="str">
+        <v>덱 조작</v>
+      </c>
+      <c r="T5" t="str">
+        <v>프로모</v>
+      </c>
+    </row>
+    <row r="6" ht="17.25" customHeight="1">
+      <c r="A6" t="str">
+        <v>아이템</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Z00005</v>
+      </c>
+      <c r="D6" t="str">
+        <v>몬스터볼</v>
+      </c>
+      <c r="I6" t="str">
+        <v>자신의 덱에서 기본 포켓몬을 랜덤으로 1장 패로 가져온다.</v>
+      </c>
+      <c r="S6" t="str">
+        <v>덱 서치</v>
+      </c>
+      <c r="T6" t="str">
+        <v>프로모</v>
+      </c>
+    </row>
+    <row r="7" ht="17.25" customHeight="1">
+      <c r="A7" t="str">
+        <v>아이템</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Z00006</v>
+      </c>
+      <c r="D7" t="str">
+        <v>레드카드</v>
+      </c>
+      <c r="I7" t="str">
+        <v>상대의 패를 모두 덱으로 되돌린다. 상대는 덱을 3장 뽑는다.</v>
+      </c>
+      <c r="S7" t="str">
+        <v>덱 드로우,패 조작,상대 패 트래쉬</v>
+      </c>
+      <c r="T7" t="str">
+        <v>프로모</v>
+      </c>
+    </row>
+    <row r="8" ht="17.25" customHeight="1">
+      <c r="A8" t="str">
+        <v>서포트</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Z00007</v>
+      </c>
+      <c r="D8" t="str">
+        <v>박사의 연구</v>
+      </c>
+      <c r="I8" t="str">
+        <v>자신의 덱을 2장 뽑는다.</v>
+      </c>
+      <c r="S8" t="str">
+        <v>덱 드로우</v>
+      </c>
+      <c r="T8" t="str">
+        <v>프로모</v>
+      </c>
+    </row>
+    <row r="9" ht="17.25" customHeight="1">
+      <c r="A9" t="str">
+        <v>물</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Z00008</v>
+      </c>
+      <c r="C9" t="str">
+        <v>ex</v>
+      </c>
+      <c r="D9" t="str">
+        <v>라프라스 ex</v>
+      </c>
+      <c r="E9" t="str">
+        <v>기본</v>
+      </c>
+      <c r="F9">
+        <v>140</v>
+      </c>
+      <c r="G9" t="str">
+        <v>버블드레인</v>
+      </c>
+      <c r="I9" t="str">
+        <v>이 포켓몬의 HP를 20회복.</v>
+      </c>
+      <c r="K9" t="str">
+        <v>물2/무색1</v>
+      </c>
+      <c r="M9">
+        <v>80</v>
+      </c>
+      <c r="O9">
+        <v>3</v>
+      </c>
+      <c r="R9" t="str">
+        <v>번개</v>
+      </c>
+      <c r="S9" t="str">
+        <v>자신 회복</v>
+      </c>
+      <c r="T9" t="str">
+        <v>프로모</v>
+      </c>
+    </row>
+    <row r="10" ht="17.25" customHeight="1">
+      <c r="A10" t="str">
+        <v>격투</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Z00009</v>
+      </c>
+      <c r="D10" t="str">
+        <v>망키</v>
+      </c>
+      <c r="E10" t="str">
+        <v>기본</v>
+      </c>
+      <c r="F10">
+        <v>50</v>
+      </c>
+      <c r="G10" t="str">
+        <v>돌격</v>
+      </c>
+      <c r="I10" t="str">
+        <v>이 포켓몬에게도 10데미지를 준다.</v>
+      </c>
+      <c r="K10" t="str">
+        <v>격투1</v>
+      </c>
+      <c r="M10">
+        <v>30</v>
+      </c>
+      <c r="O10">
+        <v>1</v>
+      </c>
+      <c r="R10" t="str">
+        <v>초</v>
+      </c>
+      <c r="S10" t="str">
+        <v>자해</v>
+      </c>
+      <c r="T10" t="str">
+        <v>프로모</v>
+      </c>
+    </row>
+    <row r="11" ht="17.25" customHeight="1">
+      <c r="A11" t="str">
+        <v>초</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Z00010</v>
+      </c>
+      <c r="D11" t="str">
+        <v>고우스트</v>
+      </c>
+      <c r="E11" t="str">
+        <v>1진화</v>
+      </c>
+      <c r="F11">
+        <v>70</v>
+      </c>
+      <c r="G11" t="str">
+        <v>허찌르기</v>
+      </c>
+      <c r="I11" t="str">
+        <v>동전을 1번 던져서 뒷면이 나오면 이 기술은 실패한다.</v>
+      </c>
+      <c r="K11" t="str">
+        <v>초1</v>
+      </c>
+      <c r="M11">
+        <v>50</v>
+      </c>
+      <c r="O11">
+        <v>1</v>
+      </c>
+      <c r="R11" t="str">
+        <v>악</v>
+      </c>
+      <c r="S11" t="str">
+        <v>동전 기술 실패 위험</v>
+      </c>
+      <c r="T11" t="str">
+        <v>프로모</v>
+      </c>
+    </row>
+    <row r="12" ht="17.25" customHeight="1">
+      <c r="A12" t="str">
+        <v>무색</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Z00011</v>
+      </c>
+      <c r="D12" t="str">
+        <v>푸린</v>
+      </c>
+      <c r="E12" t="str">
+        <v>기본</v>
+      </c>
+      <c r="F12">
+        <v>50</v>
+      </c>
+      <c r="G12" t="str">
+        <v>노래하기</v>
+      </c>
+      <c r="I12" t="str">
+        <v>상대의 배틀 포켓몬을 잠듦으로 만든다.</v>
+      </c>
+      <c r="K12" t="str">
+        <v>무색1</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>1</v>
+      </c>
+      <c r="R12" t="str">
+        <v>격투</v>
+      </c>
+      <c r="S12" t="str">
+        <v>잠듦 부여</v>
+      </c>
+      <c r="T12" t="str">
+        <v>프로모</v>
+      </c>
+    </row>
+    <row r="13" ht="17.25" customHeight="1">
+      <c r="A13" t="str">
+        <v>무색</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Z00012</v>
+      </c>
+      <c r="D13" t="str">
+        <v>이브이</v>
+      </c>
+      <c r="E13" t="str">
+        <v>기본</v>
+      </c>
+      <c r="F13">
+        <v>60</v>
+      </c>
+      <c r="G13" t="str">
+        <v>울음소리</v>
+      </c>
+      <c r="I13" t="str">
+        <v>상대의 다음 차례에 이 기술을 받은 포켓몬이 사용하는 기술의 데미지를 -20한다.</v>
+      </c>
+      <c r="K13" t="str">
+        <v>무색1</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>1</v>
+      </c>
+      <c r="R13" t="str">
+        <v>격투</v>
+      </c>
+      <c r="S13" t="str">
+        <v>데미지 감소,기술 데미지 감소 부여</v>
+      </c>
+      <c r="T13" t="str">
+        <v>프로모</v>
+      </c>
+    </row>
+    <row r="14" ht="17.25" customHeight="1">
+      <c r="A14" t="str">
+        <v>초</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Z00013</v>
+      </c>
+      <c r="C14" t="str">
+        <v>ex</v>
+      </c>
+      <c r="D14" t="str">
+        <v>크레세리아 ex</v>
+      </c>
+      <c r="E14" t="str">
+        <v>기본</v>
+      </c>
+      <c r="F14">
+        <v>140</v>
+      </c>
+      <c r="G14" t="str">
+        <v>사이코플래시</v>
+      </c>
+      <c r="K14" t="str">
+        <v>초2/무색1</v>
+      </c>
+      <c r="M14">
+        <v>80</v>
+      </c>
+      <c r="O14">
+        <v>2</v>
+      </c>
+      <c r="P14" t="str">
+        <v>초승달의 날개옷</v>
+      </c>
+      <c r="Q14" t="str">
+        <v>자신의 에너지존에서 이 포켓몬에게 초에너지를 붙일 때마다 이 포켓몬의 HP를 20회복.</v>
+      </c>
+      <c r="R14" t="str">
+        <v>악</v>
+      </c>
+      <c r="S14" t="str">
+        <v>자신 회복</v>
+      </c>
+      <c r="T14" t="str">
+        <v>프로모</v>
+      </c>
+    </row>
+    <row r="15" ht="17.25" customHeight="1">
+      <c r="A15" t="str">
+        <v>초</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Z00014</v>
+      </c>
+      <c r="D15" t="str">
+        <v>무우마</v>
+      </c>
+      <c r="E15" t="str">
+        <v>기본</v>
+      </c>
+      <c r="F15">
+        <v>60</v>
+      </c>
+      <c r="G15" t="str">
+        <v>이상한빛</v>
+      </c>
+      <c r="I15" t="str">
+        <v>상대의 배틀 포켓몬을 혼란으로 만든다.</v>
+      </c>
+      <c r="K15" t="str">
+        <v>초1</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>1</v>
+      </c>
+      <c r="R15" t="str">
+        <v>악</v>
+      </c>
+      <c r="S15" t="str">
+        <v>혼란 부여</v>
+      </c>
+      <c r="T15" t="str">
+        <v>프로모</v>
+      </c>
+    </row>
+    <row r="16" ht="17.25" customHeight="1">
+      <c r="A16" t="str">
+        <v>격투</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Z00015</v>
+      </c>
+      <c r="D16" t="str">
+        <v>코코파스</v>
+      </c>
+      <c r="E16" t="str">
+        <v>기본</v>
+      </c>
+      <c r="F16">
+        <v>60</v>
+      </c>
+      <c r="G16" t="str">
+        <v>철벽</v>
+      </c>
+      <c r="I16" t="str">
+        <v>동전을 1번 던져서 앞면이 나오면 상대의 다음 차례에 이 포켓몬은 기술의 데미지를 받지 않는다.</v>
+      </c>
+      <c r="K16" t="str">
+        <v>무색2</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>1</v>
+      </c>
+      <c r="R16" t="str">
+        <v>풀</v>
+      </c>
+      <c r="S16" t="str">
+        <v>기술 데미지 면역</v>
+      </c>
+      <c r="T16" t="str">
+        <v>프로모</v>
+      </c>
+    </row>
+    <row r="17" ht="17.25" customHeight="1">
+      <c r="A17" t="str">
+        <v>무색</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Z00016</v>
+      </c>
+      <c r="D17" t="str">
+        <v>찌르호크</v>
+      </c>
+      <c r="E17" t="str">
+        <v>2진화</v>
+      </c>
+      <c r="F17">
+        <v>140</v>
+      </c>
+      <c r="G17" t="str">
+        <v>날개치기</v>
+      </c>
+      <c r="K17" t="str">
+        <v>무색3</v>
+      </c>
+      <c r="M17">
+        <v>90</v>
+      </c>
+      <c r="O17">
+        <v>1</v>
+      </c>
+      <c r="P17" t="str">
+        <v>선풍 가드</v>
+      </c>
+      <c r="Q17" t="str">
+        <v>이 포켓몬이 격투포켓몬으로부터받는 기술의 데미지를 -30한다.</v>
+      </c>
+      <c r="R17" t="str">
+        <v>번개</v>
+      </c>
+      <c r="S17" t="str">
+        <v>데미지 감소</v>
+      </c>
+      <c r="T17" t="str">
+        <v>프로모</v>
+      </c>
+    </row>
+    <row r="18" ht="17.25" customHeight="1">
+      <c r="A18" t="str">
+        <v>물</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Z00017</v>
+      </c>
+      <c r="D18" t="str">
+        <v>플로젤</v>
+      </c>
+      <c r="E18" t="str">
+        <v>1진화</v>
+      </c>
+      <c r="F18">
+        <v>100</v>
+      </c>
+      <c r="G18" t="str">
+        <v>상처때리기</v>
+      </c>
+      <c r="I18" t="str">
+        <v>상대의 배틀 포켓몬이 데미지를 받고 있다면 60데미지를 추가한다.</v>
+      </c>
+      <c r="K18" t="str">
+        <v>물1</v>
+      </c>
+      <c r="M18" t="str">
+        <v>10+</v>
+      </c>
+      <c r="O18">
+        <v>1</v>
+      </c>
+      <c r="R18" t="str">
+        <v>번개</v>
+      </c>
+      <c r="S18" t="str">
+        <v>HP 기반 피해</v>
+      </c>
+      <c r="T18" t="str">
+        <v>프로모</v>
+      </c>
+    </row>
+    <row r="19" ht="17.25" customHeight="1">
+      <c r="A19" t="str">
+        <v>악</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Z00018</v>
+      </c>
+      <c r="D19" t="str">
+        <v>아보</v>
+      </c>
+      <c r="E19" t="str">
+        <v>기본</v>
+      </c>
+      <c r="F19">
+        <v>60</v>
+      </c>
+      <c r="G19" t="str">
+        <v>독침</v>
+      </c>
+      <c r="I19" t="str">
+        <v>상대의 배틀 포켓몬을 독으로 만든다.</v>
+      </c>
+      <c r="K19" t="str">
+        <v>악1</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>1</v>
+      </c>
+      <c r="R19" t="str">
+        <v>격투</v>
+      </c>
+      <c r="S19" t="str">
+        <v>독 부여</v>
+      </c>
+      <c r="T19" t="str">
+        <v>프로모</v>
+      </c>
+    </row>
+    <row r="20" ht="17.25" customHeight="1">
+      <c r="A20" t="str">
+        <v>무색</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Z00019</v>
+      </c>
+      <c r="D20" t="str">
+        <v>레쿠쟈</v>
+      </c>
+      <c r="E20" t="str">
+        <v>기본</v>
+      </c>
+      <c r="F20">
+        <v>100</v>
+      </c>
+      <c r="G20" t="str">
+        <v>스파이럴러시</v>
+      </c>
+      <c r="I20" t="str">
+        <v>뒷면이 나올 때까지 동전을 던져서 앞면이 나온 수 × 30데미지를 추가한다.</v>
+      </c>
+      <c r="K20" t="str">
+        <v>무색4</v>
+      </c>
+      <c r="M20" t="str">
+        <v>70+</v>
+      </c>
+      <c r="O20">
+        <v>1</v>
+      </c>
+      <c r="R20" t="str">
+        <v>번개</v>
+      </c>
+      <c r="S20" t="str">
+        <v>동전 기반 피해</v>
+      </c>
+      <c r="T20" t="str">
+        <v>프로모</v>
+      </c>
+    </row>
+    <row r="21" ht="17.25" customHeight="1">
+      <c r="A21" t="str">
+        <v>무색</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Z00020</v>
+      </c>
+      <c r="C21" t="str">
+        <v>ex</v>
+      </c>
+      <c r="D21" t="str">
+        <v>레쿠쟈 ex</v>
+      </c>
+      <c r="E21" t="str">
+        <v>기본</v>
+      </c>
+      <c r="F21">
+        <v>140</v>
+      </c>
+      <c r="G21" t="str">
+        <v>용성군</v>
+      </c>
+      <c r="I21" t="str">
+        <v>상대의 포켓몬이 랜덤으로 4번 선택되어 선택된 포켓몬 전원에게 선택된 횟수 × 40데미지를 준다.</v>
+      </c>
+      <c r="K21" t="str">
+        <v>무색4</v>
+      </c>
+      <c r="M21">
+        <v>200</v>
+      </c>
+      <c r="O21">
+        <v>2</v>
+      </c>
+      <c r="R21" t="str">
+        <v>번개</v>
+      </c>
+      <c r="S21" t="str">
+        <v>랜덤 범위 피해</v>
+      </c>
+      <c r="T21" t="str">
+        <v>프로모</v>
+      </c>
+    </row>
+    <row r="22" ht="17.25" customHeight="1">
+      <c r="A22" t="str">
+        <v>악</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Z00021</v>
+      </c>
+      <c r="D22" t="str">
+        <v>알로라 질퍽이</v>
+      </c>
+      <c r="E22" t="str">
+        <v>기본</v>
+      </c>
+      <c r="F22">
+        <v>70</v>
+      </c>
+      <c r="G22" t="str">
+        <v>독가스</v>
+      </c>
+      <c r="I22" t="str">
+        <v>상대의 배틀 포켓몬을 독으로 만든다.</v>
+      </c>
+      <c r="K22" t="str">
+        <v>악1</v>
+      </c>
+      <c r="M22">
+        <v>70</v>
+      </c>
+      <c r="O22">
+        <v>2</v>
+      </c>
+      <c r="R22" t="str">
+        <v>격투</v>
+      </c>
+      <c r="S22" t="str">
+        <v>독 부여</v>
+      </c>
+      <c r="T22" t="str">
+        <v>프로모</v>
+      </c>
+    </row>
+    <row r="23" ht="17.25" customHeight="1">
+      <c r="A23" t="str">
+        <v>무색</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Z00022</v>
+      </c>
+      <c r="D23" t="str">
+        <v>왕큰부리</v>
+      </c>
+      <c r="E23" t="str">
+        <v>2진화</v>
+      </c>
+      <c r="F23">
+        <v>140</v>
+      </c>
+      <c r="G23" t="str">
+        <v>부리캐논</v>
+      </c>
+      <c r="I23" t="str">
+        <v>동전을 1번 던져서 앞면이 나오면 상대의 배틀 포켓몬을 화상으로 만든다.</v>
+      </c>
+      <c r="K23" t="str">
+        <v>무색2</v>
+      </c>
+      <c r="M23">
+        <v>80</v>
+      </c>
+      <c r="O23">
+        <v>2</v>
+      </c>
+      <c r="R23" t="str">
+        <v>번개</v>
+      </c>
+      <c r="S23" t="str">
+        <v>화상 부여</v>
+      </c>
+      <c r="T23" t="str">
+        <v>프로모</v>
+      </c>
+    </row>
+    <row r="24" ht="17.25" customHeight="1">
+      <c r="A24" t="str">
+        <v>초</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Z00023</v>
+      </c>
+      <c r="C24" t="str">
+        <v>울트라비스트</v>
+      </c>
+      <c r="D24" t="str">
+        <v>네크로즈마 새벽의 날개</v>
+      </c>
+      <c r="E24" t="str">
+        <v>기본</v>
+      </c>
+      <c r="F24">
+        <v>110</v>
+      </c>
+      <c r="G24" t="str">
+        <v>사이코빌리</v>
+      </c>
+      <c r="I24" t="str">
+        <v>이 포켓몬에게도 30데미지를 준다.</v>
+      </c>
+      <c r="K24" t="str">
+        <v>초1/무색2</v>
+      </c>
+      <c r="M24">
+        <v>100</v>
+      </c>
+      <c r="O24">
+        <v>2</v>
+      </c>
+      <c r="R24" t="str">
+        <v>악</v>
+      </c>
+      <c r="S24" t="str">
+        <v>자해</v>
+      </c>
+      <c r="T24" t="str">
+        <v>프로모</v>
+      </c>
+    </row>
+    <row r="25" ht="17.25" customHeight="1">
+      <c r="A25" t="str">
+        <v>강철</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Z00024</v>
+      </c>
+      <c r="C25" t="str">
+        <v>울트라비스트</v>
+      </c>
+      <c r="D25" t="str">
+        <v>네크로즈마 황혼의 갈기</v>
+      </c>
+      <c r="E25" t="str">
+        <v>기본</v>
+      </c>
+      <c r="F25">
+        <v>110</v>
+      </c>
+      <c r="G25" t="str">
+        <v>블랙메탈</v>
+      </c>
+      <c r="I25" t="str">
+        <v>이 포켓몬에서 강철에너지를 1개 트래쉬한다.</v>
+      </c>
+      <c r="K25" t="str">
+        <v>강철1/무색2</v>
+      </c>
+      <c r="M25">
+        <v>100</v>
+      </c>
+      <c r="O25">
+        <v>2</v>
+      </c>
+      <c r="R25" t="str">
+        <v>불</v>
+      </c>
+      <c r="S25" t="str">
+        <v>에너지 트래쉬</v>
+      </c>
+      <c r="T25" t="str">
+        <v>프로모</v>
+      </c>
+    </row>
+    <row r="26" ht="17.25" customHeight="1">
+      <c r="A26" t="str">
+        <v>드래곤</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Z00025</v>
+      </c>
+      <c r="C26" t="str">
+        <v>울트라비스트,ex</v>
+      </c>
+      <c r="D26" t="str">
+        <v>울트라네크로즈마 ex</v>
+      </c>
+      <c r="E26" t="str">
+        <v>기본</v>
+      </c>
+      <c r="F26">
+        <v>150</v>
+      </c>
+      <c r="G26" t="str">
+        <v>포튼클로</v>
+      </c>
+      <c r="H26" t="str">
+        <v>슈게이즈</v>
+      </c>
+      <c r="J26" t="str">
+        <v>서로의 덱을 위에서부터 5장씩 트래쉬한다.</v>
+      </c>
+      <c r="K26" t="str">
+        <v>무색3</v>
+      </c>
+      <c r="L26" t="str">
+        <v>초2/강철2</v>
+      </c>
+      <c r="M26">
+        <v>60</v>
+      </c>
+      <c r="N26">
+        <v>120</v>
+      </c>
+      <c r="O26">
+        <v>2</v>
+      </c>
+      <c r="S26" t="str">
+        <v>덱 파괴,자신 덱 트래쉬</v>
+      </c>
+      <c r="T26" t="str">
+        <v>프로모</v>
+      </c>
+    </row>
+    <row r="27" ht="17.25" customHeight="1">
+      <c r="A27" t="str">
+        <v>드래곤</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Z00026</v>
+      </c>
+      <c r="D27" t="str">
+        <v>신뇽</v>
+      </c>
+      <c r="E27" t="str">
+        <v>1진화</v>
+      </c>
+      <c r="F27">
+        <v>100</v>
+      </c>
+      <c r="G27" t="str">
+        <v>탈피</v>
+      </c>
+      <c r="I27" t="str">
+        <v>이 포켓몬의 HP를 30회복.</v>
+      </c>
+      <c r="K27" t="str">
+        <v>무색1</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>2</v>
+      </c>
+      <c r="S27" t="str">
+        <v>자신 회복</v>
+      </c>
+      <c r="T27" t="str">
+        <v>프로모</v>
+      </c>
+    </row>
+    <row r="28" ht="17.25" customHeight="1">
+      <c r="A28" t="str">
+        <v>무색</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Z00027</v>
+      </c>
+      <c r="D28" t="str">
+        <v>다부니</v>
+      </c>
+      <c r="E28" t="str">
+        <v>기본</v>
+      </c>
+      <c r="F28">
+        <v>100</v>
+      </c>
+      <c r="G28" t="str">
+        <v>드레인 뺨치기</v>
+      </c>
+      <c r="I28" t="str">
+        <v>이 포켓몬의 HP를 10회복.</v>
+      </c>
+      <c r="K28" t="str">
+        <v>무색2</v>
+      </c>
+      <c r="M28">
+        <v>40</v>
+      </c>
+      <c r="O28">
+        <v>2</v>
+      </c>
+      <c r="R28" t="str">
+        <v>격투</v>
+      </c>
+      <c r="S28" t="str">
+        <v>자신 회복</v>
+      </c>
+      <c r="T28" t="str">
+        <v>프로모</v>
+      </c>
+    </row>
+    <row r="29" ht="17.25" customHeight="1">
+      <c r="A29" t="str">
+        <v>물</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Z00028</v>
+      </c>
+      <c r="D29" t="str">
+        <v>쏘드라</v>
+      </c>
+      <c r="E29" t="str">
+        <v>기본</v>
+      </c>
+      <c r="F29">
+        <v>60</v>
+      </c>
+      <c r="G29" t="str">
+        <v>워터애로</v>
+      </c>
+      <c r="I29" t="str">
+        <v>상대의 포켓몬 1마리에게 10데미지를 준다.</v>
+      </c>
+      <c r="K29" t="str">
+        <v>물1</v>
+      </c>
+      <c r="M29">
+        <v>10</v>
+      </c>
+      <c r="O29">
+        <v>1</v>
+      </c>
+      <c r="R29" t="str">
+        <v>번개</v>
+      </c>
+      <c r="S29" t="str">
+        <v>벤치 타겟 피해</v>
+      </c>
+      <c r="T29" t="str">
+        <v>프로모</v>
+      </c>
+    </row>
+    <row r="30" ht="17.25" customHeight="1">
+      <c r="A30" t="str">
+        <v>번개</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Z00029</v>
+      </c>
+      <c r="D30" t="str">
+        <v>초라기</v>
+      </c>
+      <c r="E30" t="str">
+        <v>기본</v>
+      </c>
+      <c r="F30">
+        <v>60</v>
+      </c>
+      <c r="G30" t="str">
+        <v>유인하는빛</v>
+      </c>
+      <c r="I30" t="str">
+        <v>동전을 1번 던져서 앞면이 나오면 상대의 벤치 포켓몬을 1마리 선택해서 배틀 포켓몬과 교체한다.</v>
+      </c>
+      <c r="K30" t="str">
+        <v>번개1</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>1</v>
+      </c>
+      <c r="R30" t="str">
+        <v>격투</v>
+      </c>
+      <c r="S30" t="str">
+        <v>상대 강제 교체</v>
+      </c>
+      <c r="T30" t="str">
+        <v>프로모</v>
+      </c>
+    </row>
+    <row r="31" ht="17.25" customHeight="1">
+      <c r="A31" t="str">
+        <v>무색</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Z00030</v>
+      </c>
+      <c r="C31" t="str">
+        <v>ex</v>
+      </c>
+      <c r="D31" t="str">
+        <v>해피너스 ex</v>
+      </c>
+      <c r="E31" t="str">
+        <v>1진화</v>
+      </c>
+      <c r="F31">
+        <v>180</v>
+      </c>
+      <c r="G31" t="str">
+        <v>행복펀치</v>
+      </c>
+      <c r="I31" t="str">
+        <v>동전을 1번 던져서 앞면이 나오면 이 포켓몬의 HP를 60회복.</v>
+      </c>
+      <c r="K31" t="str">
+        <v>무색4</v>
+      </c>
+      <c r="M31">
+        <v>100</v>
+      </c>
+      <c r="O31">
+        <v>3</v>
+      </c>
+      <c r="R31" t="str">
+        <v>격투</v>
+      </c>
+      <c r="S31" t="str">
+        <v>자신 회복</v>
+      </c>
+      <c r="T31" t="str">
+        <v>프로모</v>
+      </c>
+    </row>
+    <row r="32" ht="17.25" customHeight="1">
+      <c r="A32" t="str">
+        <v>풀</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Z00031</v>
+      </c>
+      <c r="D32" t="str">
+        <v>트로피우스</v>
+      </c>
+      <c r="E32" t="str">
+        <v>기본</v>
+      </c>
+      <c r="F32">
+        <v>100</v>
+      </c>
+      <c r="G32" t="str">
+        <v>더블스매시</v>
+      </c>
+      <c r="I32" t="str">
+        <v>동전을 2번 던져서 앞면이 나온 수 × 40데미지를 준다.</v>
+      </c>
+      <c r="K32" t="str">
+        <v>무색2</v>
+      </c>
+      <c r="M32" t="str">
+        <v>40×</v>
+      </c>
+      <c r="O32">
+        <v>2</v>
+      </c>
+      <c r="R32" t="str">
+        <v>불</v>
+      </c>
+      <c r="S32" t="str">
+        <v>동전 기반 피해</v>
+      </c>
+      <c r="T32" t="str">
+        <v>프로모</v>
+      </c>
+    </row>
+    <row r="33" ht="17.25" customHeight="1">
+      <c r="A33" t="str">
+        <v>물</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Z00032</v>
+      </c>
+      <c r="D33" t="str">
+        <v>발챙이</v>
+      </c>
+      <c r="E33" t="str">
+        <v>기본</v>
+      </c>
+      <c r="F33">
+        <v>60</v>
+      </c>
+      <c r="G33" t="str">
+        <v>허찌르기</v>
+      </c>
+      <c r="I33" t="str">
+        <v>동전을 1번 던져서 뒷면이 나오면 이 기술은 실패한다.</v>
+      </c>
+      <c r="K33" t="str">
+        <v>무색1</v>
+      </c>
+      <c r="M33">
+        <v>40</v>
+      </c>
+      <c r="O33">
+        <v>1</v>
+      </c>
+      <c r="R33" t="str">
+        <v>번개</v>
+      </c>
+      <c r="S33" t="str">
+        <v>동전 기술 실패 위험</v>
+      </c>
+      <c r="T33" t="str">
+        <v>프로모</v>
+      </c>
+    </row>
+    <row r="34" ht="17.25" customHeight="1">
+      <c r="A34" t="str">
+        <v>번개</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Z00033</v>
+      </c>
+      <c r="D34" t="str">
+        <v>피카츄</v>
+      </c>
+      <c r="E34" t="str">
+        <v>기본</v>
+      </c>
+      <c r="F34">
+        <v>60</v>
+      </c>
+      <c r="G34" t="str">
+        <v>전광석화</v>
+      </c>
+      <c r="I34" t="str">
+        <v>동전을 1번 던져서 앞면이 나오면 30데미지를 추가한다.</v>
+      </c>
+      <c r="K34" t="str">
+        <v>번개1/무색1</v>
+      </c>
+      <c r="M34" t="str">
+        <v>20+</v>
+      </c>
+      <c r="O34">
+        <v>1</v>
+      </c>
+      <c r="R34" t="str">
+        <v>격투</v>
+      </c>
+      <c r="S34" t="str">
+        <v>동전 기반 피해</v>
+      </c>
+      <c r="T34" t="str">
+        <v>프로모</v>
+      </c>
+    </row>
+    <row r="35" ht="17.25" customHeight="1">
+      <c r="A35" t="str">
+        <v>번개</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Z00034</v>
+      </c>
+      <c r="C35" t="str">
+        <v>ex</v>
+      </c>
+      <c r="D35" t="str">
+        <v>라이츄 ex</v>
+      </c>
+      <c r="E35" t="str">
+        <v>1진화</v>
+      </c>
+      <c r="F35">
+        <v>140</v>
+      </c>
+      <c r="G35" t="str">
+        <v>볼트태클</v>
+      </c>
+      <c r="I35" t="str">
+        <v>이 포켓몬에게도 30데미지를 준다.</v>
+      </c>
+      <c r="K35" t="str">
+        <v>번개3</v>
+      </c>
+      <c r="M35">
+        <v>130</v>
+      </c>
+      <c r="O35">
+        <v>1</v>
+      </c>
+      <c r="R35" t="str">
+        <v>격투</v>
+      </c>
+      <c r="S35" t="str">
+        <v>자해</v>
+      </c>
+      <c r="T35" t="str">
+        <v>프로모</v>
+      </c>
+    </row>
+    <row r="36" ht="17.25" customHeight="1">
+      <c r="A36" t="str">
+        <v>격투</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Z00035</v>
+      </c>
+      <c r="D36" t="str">
+        <v>괴력몬</v>
+      </c>
+      <c r="E36" t="str">
+        <v>2진화</v>
+      </c>
+      <c r="F36">
+        <v>150</v>
+      </c>
+      <c r="G36" t="str">
+        <v>허리케인펀치</v>
+      </c>
+      <c r="I36" t="str">
+        <v>동전을 4번 던져서 앞면이 나온 수 × 50데미지를 준다.</v>
+      </c>
+      <c r="K36" t="str">
+        <v>격투3</v>
+      </c>
+      <c r="M36">
+        <v>150</v>
+      </c>
+      <c r="O36">
+        <v>2</v>
+      </c>
+      <c r="R36" t="str">
+        <v>초</v>
+      </c>
+      <c r="S36" t="str">
+        <v>동전 기반 피해</v>
+      </c>
+      <c r="T36" t="str">
+        <v>프로모</v>
+      </c>
+    </row>
+    <row r="37" ht="17.25" customHeight="1">
+      <c r="A37" t="str">
+        <v>풀</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Z00036</v>
+      </c>
+      <c r="D37" t="str">
+        <v>치릴리</v>
+      </c>
+      <c r="E37" t="str">
+        <v>기본</v>
+      </c>
+      <c r="F37">
+        <v>50</v>
+      </c>
+      <c r="G37" t="str">
+        <v>허찌르기</v>
+      </c>
+      <c r="I37" t="str">
+        <v>동전을 1번 던져서 뒷면이 나오면 이 기술은 실패한다.</v>
+      </c>
+      <c r="K37" t="str">
+        <v>풀1</v>
+      </c>
+      <c r="M37">
+        <v>30</v>
+      </c>
+      <c r="O37">
+        <v>1</v>
+      </c>
+      <c r="R37" t="str">
+        <v>불</v>
+      </c>
+      <c r="S37" t="str">
+        <v>동전 기술 실패 위험</v>
+      </c>
+      <c r="T37" t="str">
+        <v>프로모</v>
+      </c>
+    </row>
+    <row r="38" ht="17.25" customHeight="1">
+      <c r="A38" t="str">
+        <v>물</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Z00037</v>
+      </c>
+      <c r="D38" t="str">
+        <v>개구마르</v>
+      </c>
+      <c r="E38" t="str">
+        <v>기본</v>
+      </c>
+      <c r="F38">
+        <v>60</v>
+      </c>
+      <c r="G38" t="str">
+        <v>거품</v>
+      </c>
+      <c r="I38" t="str">
+        <v>동전을 1번 던져서 앞면이 나오면 상대의 배틀 포켓몬을 마비로 만든다.</v>
+      </c>
+      <c r="K38" t="str">
+        <v>물2</v>
+      </c>
+      <c r="M38">
+        <v>20</v>
+      </c>
+      <c r="O38">
+        <v>1</v>
+      </c>
+      <c r="R38" t="str">
+        <v>번개</v>
+      </c>
+      <c r="S38" t="str">
+        <v>마비 부여,동전 상태이상</v>
+      </c>
+      <c r="T38" t="str">
+        <v>프로모</v>
+      </c>
+    </row>
+    <row r="39" ht="17.25" customHeight="1">
+      <c r="A39" t="str">
+        <v>무색</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Z00038</v>
+      </c>
+      <c r="C39" t="str">
+        <v>메가ex</v>
+      </c>
+      <c r="D39" t="str">
+        <v>메가피죤투 ex</v>
+      </c>
+      <c r="E39" t="str">
+        <v>2진화</v>
+      </c>
+      <c r="F39">
+        <v>210</v>
+      </c>
+      <c r="G39" t="str">
+        <v>자이언트 트위스터</v>
+      </c>
+      <c r="I39" t="str">
+        <v>동전을 3번 던져서 앞면이 나온 수만큼 상대의 배틀 포켓몬에서 에너지를 랜덤으로 트래쉬한다. 모두 뒷면이 나오면 이 기술은 실패한다.</v>
+      </c>
+      <c r="K39" t="str">
+        <v>무색3</v>
+      </c>
+      <c r="M39">
+        <v>100</v>
+      </c>
+      <c r="O39">
+        <v>2</v>
+      </c>
+      <c r="R39" t="str">
+        <v>번개</v>
+      </c>
+      <c r="S39" t="str">
+        <v>상대 에너지 트래쉬,동전 기술 실패 위험</v>
+      </c>
+      <c r="T39" t="str">
+        <v>프로모</v>
+      </c>
+    </row>
+    <row r="40" ht="17.25" customHeight="1">
+      <c r="A40" t="str">
+        <v>물</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Z00039</v>
+      </c>
+      <c r="D40" t="str">
+        <v>잉어킹</v>
+      </c>
+      <c r="E40" t="str">
+        <v>기본</v>
+      </c>
+      <c r="F40">
+        <v>30</v>
+      </c>
+      <c r="G40" t="str">
+        <v>튀어오르기 고수</v>
+      </c>
+      <c r="I40" t="str">
+        <v>동전을 2번 던져서 앞면이 나오면 20데미지를 추가한다.</v>
+      </c>
+      <c r="K40" t="str">
+        <v>물1</v>
+      </c>
+      <c r="M40" t="str">
+        <v>10+</v>
+      </c>
+      <c r="O40">
+        <v>1</v>
+      </c>
+      <c r="R40" t="str">
+        <v>번개</v>
+      </c>
+      <c r="S40" t="str">
+        <v>동전 기반 피해</v>
+      </c>
+      <c r="T40" t="str">
+        <v>프로모</v>
+      </c>
+    </row>
+    <row r="41" ht="17.25" customHeight="1">
+      <c r="A41" t="str">
+        <v>무색</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Z00040</v>
+      </c>
+      <c r="D41" t="str">
+        <v>파비코</v>
+      </c>
+      <c r="E41" t="str">
+        <v>기본</v>
+      </c>
+      <c r="F41">
+        <v>50</v>
+      </c>
+      <c r="G41" t="str">
+        <v>친구찾기</v>
+      </c>
+      <c r="I41" t="str">
+        <v>자신의 덱에서 포켓몬을 랜덤으로 1장 패로 가져온다.</v>
+      </c>
+      <c r="K41" t="str">
+        <v>무색1</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="O41">
+        <v>1</v>
+      </c>
+      <c r="R41" t="str">
+        <v>번개</v>
+      </c>
+      <c r="S41" t="str">
+        <v>덱 서치</v>
+      </c>
+      <c r="T41" t="str">
+        <v>프로모</v>
+      </c>
+    </row>
+    <row r="42" ht="17.25" customHeight="1">
+      <c r="A42" t="str">
+        <v>격투</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Z00041</v>
+      </c>
+      <c r="D42" t="str">
+        <v>롱스톤</v>
+      </c>
+      <c r="E42" t="str">
+        <v>기본</v>
+      </c>
+      <c r="F42">
+        <v>100</v>
+      </c>
+      <c r="G42" t="str">
+        <v>테일스매시</v>
+      </c>
+      <c r="I42" t="str">
+        <v>동전을 1번 던져서 뒷면이 나오면 이 기술은 실패한다.</v>
+      </c>
+      <c r="K42" t="str">
+        <v>무색3</v>
+      </c>
+      <c r="M42">
+        <v>90</v>
+      </c>
+      <c r="O42">
+        <v>3</v>
+      </c>
+      <c r="R42" t="str">
+        <v>풀</v>
+      </c>
+      <c r="S42" t="str">
+        <v>동전 기술 실패 위험</v>
+      </c>
+      <c r="T42" t="str">
+        <v>프로모</v>
+      </c>
+    </row>
+    <row r="43" ht="17.25" customHeight="1">
+      <c r="A43" t="str">
+        <v>격투</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Z00042</v>
+      </c>
+      <c r="D43" t="str">
+        <v>루차불</v>
+      </c>
+      <c r="E43" t="str">
+        <v>기본</v>
+      </c>
+      <c r="F43">
+        <v>70</v>
+      </c>
+      <c r="G43" t="str">
+        <v>제비반환</v>
+      </c>
+      <c r="I43" t="str">
+        <v>동전을 1번 던져서 앞면이 나오면 30데미지를 추가한다.</v>
+      </c>
+      <c r="K43" t="str">
+        <v>무색2</v>
+      </c>
+      <c r="M43" t="str">
+        <v>40+</v>
+      </c>
+      <c r="O43">
+        <v>1</v>
+      </c>
+      <c r="R43" t="str">
+        <v>번개</v>
+      </c>
+      <c r="S43" t="str">
+        <v>동전 기반 피해</v>
+      </c>
+      <c r="T43" t="str">
+        <v>프로모</v>
+      </c>
+    </row>
+    <row r="44" ht="17.25" customHeight="1">
+      <c r="A44" t="str">
+        <v>드래곤</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Z00043</v>
+      </c>
+      <c r="C44" t="str">
+        <v>메가ex</v>
+      </c>
+      <c r="D44" t="str">
+        <v>메가라티오스 ex</v>
+      </c>
+      <c r="E44" t="str">
+        <v>기본</v>
+      </c>
+      <c r="F44">
+        <v>180</v>
+      </c>
+      <c r="G44" t="str">
+        <v>소닉임펄스</v>
+      </c>
+      <c r="I44" t="str">
+        <v>이 포켓몬에서 에너지를 모두 트래쉬한다.</v>
+      </c>
+      <c r="K44" t="str">
+        <v>물2/초1</v>
+      </c>
+      <c r="M44">
+        <v>160</v>
+      </c>
+      <c r="O44">
+        <v>2</v>
+      </c>
+      <c r="S44" t="str">
+        <v>에너지 트래쉬</v>
+      </c>
+      <c r="T44" t="str">
+        <v>프로모</v>
+      </c>
+    </row>
+    <row r="45" ht="17.25" customHeight="1">
+      <c r="A45" t="str">
+        <v>물</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Z00044</v>
+      </c>
+      <c r="D45" t="str">
+        <v>물짱이</v>
+      </c>
+      <c r="E45" t="str">
+        <v>기본</v>
+      </c>
+      <c r="F45">
+        <v>60</v>
+      </c>
+      <c r="G45" t="str">
+        <v>허찌르기</v>
+      </c>
+      <c r="I45" t="str">
+        <v>동전을 1번 던져서 뒷면이 나오면 이 기술은 실패한다.</v>
+      </c>
+      <c r="K45" t="str">
+        <v>물1</v>
+      </c>
+      <c r="M45">
+        <v>40</v>
+      </c>
+      <c r="O45">
+        <v>1</v>
+      </c>
+      <c r="R45" t="str">
+        <v>번개</v>
+      </c>
+      <c r="S45" t="str">
+        <v>동전 기술 실패 위험</v>
+      </c>
+      <c r="T45" t="str">
+        <v>프로모</v>
+      </c>
+    </row>
+    <row r="46" ht="17.25" customHeight="1">
+      <c r="A46" t="str">
+        <v>초</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Z00045</v>
+      </c>
+      <c r="D46" t="str">
+        <v>랄토스</v>
+      </c>
+      <c r="E46" t="str">
+        <v>기본</v>
+      </c>
+      <c r="F46">
+        <v>60</v>
+      </c>
+      <c r="G46" t="str">
+        <v>드레인키스</v>
+      </c>
+      <c r="I46" t="str">
+        <v>이 포켓몬의 HP를 10회복.</v>
+      </c>
+      <c r="K46" t="str">
+        <v>초1</v>
+      </c>
+      <c r="M46">
+        <v>10</v>
+      </c>
+      <c r="O46">
+        <v>1</v>
+      </c>
+      <c r="R46" t="str">
+        <v>악</v>
+      </c>
+      <c r="S46" t="str">
+        <v>자신 회복</v>
+      </c>
+      <c r="T46" t="str">
+        <v>프로모</v>
+      </c>
+    </row>
+    <row r="47" ht="17.25" customHeight="1">
+      <c r="A47" t="str">
+        <v>격투</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Z00046</v>
+      </c>
+      <c r="C47" t="str">
+        <v>메가ex</v>
+      </c>
+      <c r="D47" t="str">
+        <v>메가요가램 ex</v>
+      </c>
+      <c r="E47" t="str">
+        <v>1진화</v>
+      </c>
+      <c r="F47">
+        <v>180</v>
+      </c>
+      <c r="G47" t="str">
+        <v>차크라피스트</v>
+      </c>
+      <c r="I47" t="str">
+        <v>이 포켓몬에게 초에너지가 붙어 있다면 40데미지를 추가한다. 이 기술의 데미지는 상대의 배틀 포켓몬에게 걸려 있는 효과를 계산하지 않는다.</v>
+      </c>
+      <c r="K47" t="str">
+        <v>격투1/무색2</v>
+      </c>
+      <c r="M47" t="str">
+        <v>100+</v>
+      </c>
+      <c r="O47">
+        <v>1</v>
+      </c>
+      <c r="R47" t="str">
+        <v>초</v>
+      </c>
+      <c r="S47" t="str">
+        <v>효과 무시,에너지 기반 피해</v>
+      </c>
+      <c r="T47" t="str">
+        <v>프로모</v>
+      </c>
+    </row>
+    <row r="48" ht="17.25" customHeight="1">
+      <c r="A48" t="str">
+        <v>풀</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Z00047</v>
+      </c>
+      <c r="D48" t="str">
+        <v>미니브</v>
+      </c>
+      <c r="E48" t="str">
+        <v>기본</v>
+      </c>
+      <c r="F48">
+        <v>60</v>
+      </c>
+      <c r="G48" t="str">
+        <v>영양소</v>
+      </c>
+      <c r="I48" t="str">
+        <v>자신의 포켓몬 1마리의 HP를 20회복.</v>
+      </c>
+      <c r="K48" t="str">
+        <v>풀1</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+      <c r="O48">
+        <v>1</v>
+      </c>
+      <c r="R48" t="str">
+        <v>불</v>
+      </c>
+      <c r="S48" t="str">
+        <v>자신 회복</v>
+      </c>
+      <c r="T48" t="str">
+        <v>프로모</v>
+      </c>
+    </row>
+    <row r="49" ht="17.25" customHeight="1">
+      <c r="A49" t="str">
+        <v>물</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Z00048</v>
+      </c>
+      <c r="D49" t="str">
+        <v>드니차</v>
+      </c>
+      <c r="E49" t="str">
+        <v>기본</v>
+      </c>
+      <c r="F49">
+        <v>60</v>
+      </c>
+      <c r="G49" t="str">
+        <v>딱딱해지기</v>
+      </c>
+      <c r="I49" t="str">
+        <v>상대의 다음 차례에 이 포켓몬이 받는 기술의 데미지를 -20한다.</v>
+      </c>
+      <c r="K49" t="str">
+        <v>물1</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>1</v>
+      </c>
+      <c r="R49" t="str">
+        <v>강철</v>
+      </c>
+      <c r="S49" t="str">
+        <v>데미지 감소</v>
+      </c>
+      <c r="T49" t="str">
+        <v>프로모</v>
+      </c>
+    </row>
+    <row r="50" ht="17.25" customHeight="1">
+      <c r="A50" t="str">
+        <v>번개</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Z00049</v>
+      </c>
+      <c r="D50" t="str">
+        <v>썬더라이</v>
+      </c>
+      <c r="E50" t="str">
+        <v>기본</v>
+      </c>
+      <c r="F50">
+        <v>60</v>
+      </c>
+      <c r="G50" t="str">
+        <v>돌격</v>
+      </c>
+      <c r="I50" t="str">
+        <v>이 포켓몬에게도 10데미지를 준다.</v>
+      </c>
+      <c r="K50" t="str">
+        <v>번개1</v>
+      </c>
+      <c r="M50">
+        <v>30</v>
+      </c>
+      <c r="O50">
+        <v>1</v>
+      </c>
+      <c r="R50" t="str">
+        <v>격투</v>
+      </c>
+      <c r="S50" t="str">
+        <v>자해</v>
+      </c>
+      <c r="T50" t="str">
+        <v>프로모</v>
+      </c>
+    </row>
+    <row r="51" ht="17.25" customHeight="1">
+      <c r="A51" t="str">
+        <v>강철</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Z00050</v>
+      </c>
+      <c r="D51" t="str">
+        <v>부르롱</v>
+      </c>
+      <c r="E51" t="str">
+        <v>기본</v>
+      </c>
+      <c r="F51">
+        <v>60</v>
+      </c>
+      <c r="G51" t="str">
+        <v>독가스</v>
+      </c>
+      <c r="I51" t="str">
+        <v>상대의 배틀 포켓몬을 독으로 만든다.</v>
+      </c>
+      <c r="K51" t="str">
+        <v>강철1</v>
+      </c>
+      <c r="M51">
+        <v>0</v>
+      </c>
+      <c r="O51">
+        <v>1</v>
+      </c>
+      <c r="R51" t="str">
+        <v>불</v>
+      </c>
+      <c r="S51" t="str">
+        <v>독 부여</v>
+      </c>
+      <c r="T51" t="str">
+        <v>프로모</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T51"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -41144,6 +43154,9 @@
       </c>
       <c r="B69">
         <v>7020</v>
+      </c>
+      <c r="C69" t="str">
+        <v>울트라비스트</v>
       </c>
       <c r="D69" t="str">
         <v>전수목</v>
@@ -59444,7 +61457,7 @@
         <v>초</v>
       </c>
       <c r="S162" t="str">
-        <v>스태디움 제거</v>
+        <v>스타디움 제거</v>
       </c>
       <c r="T162" t="str">
         <v>몽환퍼레이드</v>
@@ -64013,6 +66026,9 @@
       </c>
       <c r="B68">
         <v>7044</v>
+      </c>
+      <c r="C68" t="str">
+        <v>울트라비스트</v>
       </c>
       <c r="D68" t="str">
         <v>베베놈</v>

--- a/app/data/card_list.xlsx
+++ b/app/data/card_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\project\pokemon-card-app\app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C43B0AD0-8BF1-4743-AB2C-8EBC53D814CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1466A4DF-EA85-4096-BC5E-AF5D36298A00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3300" yWindow="2475" windowWidth="28800" windowHeight="15345" firstSheet="3" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19106" uniqueCount="5428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19107" uniqueCount="5429">
   <si>
     <t>타입</t>
   </si>
@@ -16901,6 +16901,10 @@
   </si>
   <si>
     <t>p-a-007</t>
+  </si>
+  <si>
+    <t>p-b-043</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -43441,6 +43445,9 @@
       <c r="B50" t="s">
         <v>3490</v>
       </c>
+      <c r="C50" t="s">
+        <v>5428</v>
+      </c>
       <c r="E50" t="s">
         <v>1446</v>
       </c>

--- a/app/data/card_list.xlsx
+++ b/app/data/card_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\project\pokemon-card-app\app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1466A4DF-EA85-4096-BC5E-AF5D36298A00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D284C5C-9F10-4E54-A0F7-1516C59028DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3300" yWindow="2475" windowWidth="28800" windowHeight="15345" firstSheet="3" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16880,31 +16880,31 @@
     <t>a4a-007</t>
   </si>
   <si>
-    <t>p-a-001</t>
+    <t>pb-043</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>p-a-002</t>
+    <t>pa-001</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>p-a-003</t>
-  </si>
-  <si>
-    <t>p-a-004</t>
-  </si>
-  <si>
-    <t>p-a-005</t>
-  </si>
-  <si>
-    <t>p-a-006</t>
-  </si>
-  <si>
-    <t>p-a-007</t>
-  </si>
-  <si>
-    <t>p-b-043</t>
+    <t>pa-002</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>pa-003</t>
+  </si>
+  <si>
+    <t>pa-004</t>
+  </si>
+  <si>
+    <t>pa-005</t>
+  </si>
+  <si>
+    <t>pa-006</t>
+  </si>
+  <si>
+    <t>pa-007</t>
   </si>
 </sst>
 </file>
@@ -41535,7 +41535,7 @@
         <v>3376</v>
       </c>
       <c r="C2" t="s">
-        <v>5421</v>
+        <v>5422</v>
       </c>
       <c r="E2" t="s">
         <v>3377</v>
@@ -41558,7 +41558,7 @@
         <v>3380</v>
       </c>
       <c r="C3" t="s">
-        <v>5422</v>
+        <v>5423</v>
       </c>
       <c r="E3" t="s">
         <v>3381</v>
@@ -41581,7 +41581,7 @@
         <v>3383</v>
       </c>
       <c r="C4" t="s">
-        <v>5423</v>
+        <v>5424</v>
       </c>
       <c r="E4" t="s">
         <v>3384</v>
@@ -41604,7 +41604,7 @@
         <v>3385</v>
       </c>
       <c r="C5" t="s">
-        <v>5424</v>
+        <v>5425</v>
       </c>
       <c r="E5" t="s">
         <v>3386</v>
@@ -41627,7 +41627,7 @@
         <v>3388</v>
       </c>
       <c r="C6" t="s">
-        <v>5425</v>
+        <v>5426</v>
       </c>
       <c r="E6" t="s">
         <v>3389</v>
@@ -41650,7 +41650,7 @@
         <v>3391</v>
       </c>
       <c r="C7" t="s">
-        <v>5426</v>
+        <v>5427</v>
       </c>
       <c r="E7" t="s">
         <v>3392</v>
@@ -41673,7 +41673,7 @@
         <v>3395</v>
       </c>
       <c r="C8" t="s">
-        <v>5427</v>
+        <v>5428</v>
       </c>
       <c r="E8" t="s">
         <v>3396</v>
@@ -43446,7 +43446,7 @@
         <v>3490</v>
       </c>
       <c r="C50" t="s">
-        <v>5428</v>
+        <v>5421</v>
       </c>
       <c r="E50" t="s">
         <v>1446</v>

--- a/app/data/card_list.xlsx
+++ b/app/data/card_list.xlsx
@@ -22241,6 +22241,9 @@
       <c r="T252" t="str">
         <v>격투</v>
       </c>
+      <c r="U252" t="str">
+        <v>에너지 기반 피해</v>
+      </c>
       <c r="V252" t="str">
         <v>진격 패러독스</v>
       </c>
@@ -25322,6 +25325,9 @@
       <c r="E133" t="str">
         <v>이 카드를 붙이고 있는 「미래」의 포켓몬이 사용하는 기술이 상대의 배틀 포켓몬에게 주는 데미지를 +20한다.</v>
       </c>
+      <c r="F133" t="str">
+        <v>데미지 강화</v>
+      </c>
       <c r="G133" t="str">
         <v>진격 패러독스</v>
       </c>
@@ -25387,6 +25393,9 @@
       </c>
       <c r="E136" t="str">
         <v>자신의 필드의 「미래」의 포켓몬을 1마리 선택해서 덱으로 되돌린다.</v>
+      </c>
+      <c r="F136" t="str">
+        <v>자신 귀환</v>
       </c>
       <c r="G136" t="str">
         <v>진격 패러독스</v>
@@ -27846,7 +27855,6 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="17.25" customHeight="1"/>
     <row r="4" ht="17.25" customHeight="1"/>
     <row r="5" ht="17.25" customHeight="1"/>
@@ -34442,6 +34450,9 @@
       <c r="T148" t="str">
         <v>물</v>
       </c>
+      <c r="U148" t="str">
+        <v>동전 기반 피해</v>
+      </c>
       <c r="V148" t="str">
         <v>진격 패러독스</v>
       </c>
@@ -43022,7 +43033,7 @@
         <v>번개</v>
       </c>
       <c r="U195" t="str">
-        <v>상대 벤치 피해</v>
+        <v>에너지 기반 피해,상대 벤치 피해</v>
       </c>
       <c r="V195" t="str">
         <v>홍련 블레이즈</v>
@@ -50375,7 +50386,7 @@
         <v>격투</v>
       </c>
       <c r="U93" t="str">
-        <v>상대 벤치 피해</v>
+        <v>랜덤 범위 피해</v>
       </c>
       <c r="V93" t="str">
         <v>메가라이징</v>
@@ -50425,7 +50436,7 @@
         <v>격투</v>
       </c>
       <c r="U94" t="str">
-        <v>상대 벤치 피해</v>
+        <v>랜덤 범위 피해</v>
       </c>
       <c r="V94" t="str">
         <v>메가라이징</v>
@@ -62098,6 +62109,9 @@
       <c r="T208" t="str">
         <v>악</v>
       </c>
+      <c r="U208" t="str">
+        <v>잠듦 부여</v>
+      </c>
       <c r="V208" t="str">
         <v>진격 패러독스</v>
       </c>
@@ -62185,6 +62199,9 @@
       </c>
       <c r="T210" t="str">
         <v>악</v>
+      </c>
+      <c r="U210" t="str">
+        <v>피격 데미지 증가</v>
       </c>
       <c r="V210" t="str">
         <v>진격 패러독스</v>
@@ -79733,6 +79750,9 @@
       <c r="T176" t="str">
         <v>풀</v>
       </c>
+      <c r="U176" t="str">
+        <v>기절 복수 피해</v>
+      </c>
       <c r="V176" t="str">
         <v>진격 패러독스</v>
       </c>
@@ -79920,6 +79940,9 @@
       </c>
       <c r="T180" t="str">
         <v>풀</v>
+      </c>
+      <c r="U180" t="str">
+        <v>상대 강제 교체</v>
       </c>
       <c r="V180" t="str">
         <v>진격 패러독스</v>
@@ -84688,6 +84711,9 @@
       <c r="T107" t="str">
         <v>불</v>
       </c>
+      <c r="U107" t="str">
+        <v>동전 기반 피해</v>
+      </c>
       <c r="V107" t="str">
         <v>진격 패러독스</v>
       </c>
